--- a/Data/CERP_PBC_Summary_Data.xlsx
+++ b/Data/CERP_PBC_Summary_Data.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="501">
   <si>
     <t>CR-E1_LiveMean</t>
   </si>
@@ -1526,6 +1526,9 @@
   <si>
     <t>Summer 2026</t>
   </si>
+  <si>
+    <t xml:space="preserve">Fall 2026</t>
+  </si>
 </sst>
 </file>
 
@@ -12209,6 +12212,777 @@
         <v>0</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>46217</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E41" t="n">
+        <v>20</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H41" t="n">
+        <v>40</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>46217</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="L41" t="n">
+        <v>60</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="O41" t="n">
+        <v>20</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S41" t="n">
+        <v>40</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V41" t="n">
+        <v>40</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z41" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>60</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT41" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>100</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>60</v>
+      </c>
+      <c r="BD41" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>60</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BI41" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ41" t="n">
+        <v>60</v>
+      </c>
+      <c r="BK41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BM41" t="n">
+        <v>40</v>
+      </c>
+      <c r="BN41" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="BO41" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BP41" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BQ41" t="n">
+        <v>60</v>
+      </c>
+      <c r="BR41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BS41" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BT41" t="n">
+        <v>40</v>
+      </c>
+      <c r="BU41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BV41" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BW41" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX41" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="BY41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BZ41" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="CA41" t="n">
+        <v>20</v>
+      </c>
+      <c r="CB41" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="CC41" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="CD41" t="n">
+        <v>60</v>
+      </c>
+      <c r="CE41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="CF41" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="CG41" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H42" t="n">
+        <v>60</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L42" t="n">
+        <v>60</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="O42" t="n">
+        <v>80</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S42" t="n">
+        <v>80</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="V42" t="n">
+        <v>80</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ42" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>80</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT42" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>80</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD42" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>60</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BJ42" t="n">
+        <v>80</v>
+      </c>
+      <c r="BK42" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BL42" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BM42" t="n">
+        <v>20</v>
+      </c>
+      <c r="BN42" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR42" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BS42" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BT42" t="n">
+        <v>20</v>
+      </c>
+      <c r="BU42" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BV42" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BW42" t="n">
+        <v>20</v>
+      </c>
+      <c r="BX42" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BY42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BZ42" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="CA42" t="n">
+        <v>60</v>
+      </c>
+      <c r="CB42" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="CC42" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="CD42" t="n">
+        <v>20</v>
+      </c>
+      <c r="CE42" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CF42" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="CG42" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H43" t="n">
+        <v>80</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L43" t="n">
+        <v>60</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="O43" t="n">
+        <v>60</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="S43" t="n">
+        <v>40</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="V43" t="n">
+        <v>80</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT43" s="3" t="n">
+        <v>46268</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>80</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD43" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>80</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BI43" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BJ43" t="n">
+        <v>20</v>
+      </c>
+      <c r="BK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN43" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="BO43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BP43" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BQ43" t="n">
+        <v>20</v>
+      </c>
+      <c r="BR43" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BS43" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BT43" t="n">
+        <v>20</v>
+      </c>
+      <c r="BU43" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BV43" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BW43" t="n">
+        <v>60</v>
+      </c>
+      <c r="BX43" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="BY43" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BZ43" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CA43" t="n">
+        <v>80</v>
+      </c>
+      <c r="CB43" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="CC43" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="CD43" t="n">
+        <v>80</v>
+      </c>
+      <c r="CE43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="CF43" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="CG43" t="n">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -14896,6 +15670,314 @@
         <v>0.03</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>500</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C15" t="n">
+        <v>59.47</v>
+      </c>
+      <c r="D15" t="n">
+        <v>77.96</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1073.33</v>
+      </c>
+      <c r="H15" t="n">
+        <v>572.6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="K15" t="n">
+        <v>324.27</v>
+      </c>
+      <c r="L15" t="n">
+        <v>173.59</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="O15" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="P15" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="S15" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="T15" t="n">
+        <v>91.69</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W15" t="n">
+        <v>481.14</v>
+      </c>
+      <c r="X15" t="n">
+        <v>219.37</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>34.13</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>453.87</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>429.9</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>214.93</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>157.71</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>133.33</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>78.06</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>586.57</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>784.12</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>158</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>220.77</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>638.67</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>646.07</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>266</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>240.39</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>411.43</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>232.78</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>36.27</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>22.55</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>500.27</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>304.33</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>36.62</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>74.67</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>60.68</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>76.57</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>42.33</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>37.87</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>374.93</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>99.01</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -16032,6 +17114,122 @@
       </c>
       <c r="AD14" t="n">
         <v>0.03</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>500</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C15" t="n">
+        <v>566.4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>653.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G15" t="n">
+        <v>192.53</v>
+      </c>
+      <c r="H15" t="n">
+        <v>186.55</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K15" t="n">
+        <v>180</v>
+      </c>
+      <c r="L15" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="O15" t="n">
+        <v>267.38</v>
+      </c>
+      <c r="P15" t="n">
+        <v>295.93</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="S15" t="n">
+        <v>465.21</v>
+      </c>
+      <c r="T15" t="n">
+        <v>625.81</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="W15" t="n">
+        <v>98.05</v>
+      </c>
+      <c r="X15" t="n">
+        <v>183.98</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>313.82</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>298</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>63.52</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>48.34</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>145.33</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>174.47</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.13</v>
       </c>
     </row>
   </sheetData>
@@ -17388,6 +18586,164 @@
         <v>19.010000000000002</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>500</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C15" t="n">
+        <v>38.87</v>
+      </c>
+      <c r="D15" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="E15" t="n">
+        <v>31.85</v>
+      </c>
+      <c r="F15" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="G15" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="H15" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="I15" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="J15" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="K15" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="L15" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="M15" t="n">
+        <v>35.42</v>
+      </c>
+      <c r="N15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>33.83</v>
+      </c>
+      <c r="R15" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="S15" t="n">
+        <v>33.68</v>
+      </c>
+      <c r="T15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="V15" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="W15" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="X15" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>39.21</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>21.41</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>47.13</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>35.59</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>47.92</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>44.19</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>53.11</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>23.03</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>58.41</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>79.65</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>20.96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -18018,6 +19374,68 @@
       </c>
       <c r="P14" t="n">
         <v>19.010000000000002</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>500</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C15" t="n">
+        <v>34.37</v>
+      </c>
+      <c r="D15" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="E15" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="F15" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="G15" t="n">
+        <v>29.62</v>
+      </c>
+      <c r="H15" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="I15" t="n">
+        <v>34.12</v>
+      </c>
+      <c r="J15" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="K15" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="L15" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="M15" t="n">
+        <v>34.19</v>
+      </c>
+      <c r="N15" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="O15" t="n">
+        <v>36.95</v>
+      </c>
+      <c r="P15" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>48.58</v>
+      </c>
+      <c r="R15" t="n">
+        <v>20.61</v>
+      </c>
+      <c r="S15" t="n">
+        <v>64.12</v>
+      </c>
+      <c r="T15" t="n">
+        <v>25.13</v>
       </c>
     </row>
   </sheetData>
@@ -22581,6 +23999,345 @@
       </c>
       <c r="AK40" t="n">
         <v>40</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>46217</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="E41" t="n">
+        <v>30</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>46217</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I41" t="n">
+        <v>40</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M41" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>40</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="U41" t="n">
+        <v>40</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="Z41" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="AD41" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="AH41" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.94</v>
+      </c>
+      <c r="E42" t="n">
+        <v>30</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.94</v>
+      </c>
+      <c r="I42" t="n">
+        <v>70</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="M42" t="n">
+        <v>86.67</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>80</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U42" t="n">
+        <v>73.33</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>73.33</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="AD42" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="AH42" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="E43" t="n">
+        <v>40</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I43" t="n">
+        <v>60</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M43" t="n">
+        <v>60</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>40</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="U43" t="n">
+        <v>60</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>46268</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="AD43" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="AH43" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>66.67</v>
       </c>
     </row>
   </sheetData>
@@ -30346,6 +32103,597 @@
         <v>0</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>46217</v>
+      </c>
+      <c r="C41" t="n">
+        <v>65.63</v>
+      </c>
+      <c r="D41" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="E41" t="n">
+        <v>79.81</v>
+      </c>
+      <c r="F41" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="G41" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="H41" t="n">
+        <v>68.67</v>
+      </c>
+      <c r="I41" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="J41" t="n">
+        <v>77.22</v>
+      </c>
+      <c r="K41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="L41" t="n">
+        <v>40</v>
+      </c>
+      <c r="M41" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N41" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="O41" t="n">
+        <v>82</v>
+      </c>
+      <c r="P41" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>46217</v>
+      </c>
+      <c r="S41" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="T41" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="U41" t="n">
+        <v>56.12</v>
+      </c>
+      <c r="V41" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="W41" t="n">
+        <v>20</v>
+      </c>
+      <c r="X41" t="n">
+        <v>53.43</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>53.36</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>50.43</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>8.54</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="AH41" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>52.07</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>64.08</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX41" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>77.21</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>63.62</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="BI41" t="n">
+        <v>72.27</v>
+      </c>
+      <c r="BJ41" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="BK41" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>9.36</v>
+      </c>
+      <c r="BM41" t="n">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C42" t="n">
+        <v>67.83</v>
+      </c>
+      <c r="D42" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="E42" t="n">
+        <v>82.29</v>
+      </c>
+      <c r="F42" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G42" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="H42" t="n">
+        <v>70.27</v>
+      </c>
+      <c r="I42" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="J42" t="n">
+        <v>73.05</v>
+      </c>
+      <c r="K42" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="L42" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="M42" t="n">
+        <v>72.17</v>
+      </c>
+      <c r="N42" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="O42" t="n">
+        <v>75.64</v>
+      </c>
+      <c r="P42" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="S42" t="n">
+        <v>53.47</v>
+      </c>
+      <c r="T42" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="U42" t="n">
+        <v>53</v>
+      </c>
+      <c r="V42" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="W42" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="X42" t="n">
+        <v>51.73</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>9.2</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>53.29</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>9.39</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="AH42" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>55.17</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>57.83</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>57.86</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>58.64</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="AX42" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>86.1</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>62.83</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>8.78</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BJ42" t="n">
+        <v>9.47</v>
+      </c>
+      <c r="BK42" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="BL42" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="BM42" t="n">
+        <v>46.67</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C43" t="n">
+        <v>73.6</v>
+      </c>
+      <c r="D43" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="E43" t="n">
+        <v>76.74</v>
+      </c>
+      <c r="F43" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="G43" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="H43" t="n">
+        <v>68</v>
+      </c>
+      <c r="I43" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="J43" t="n">
+        <v>75.26</v>
+      </c>
+      <c r="K43" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="L43" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="M43" t="n">
+        <v>69.43</v>
+      </c>
+      <c r="N43" t="n">
+        <v>16.23</v>
+      </c>
+      <c r="O43" t="n">
+        <v>74.38</v>
+      </c>
+      <c r="P43" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>30</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="S43" t="n">
+        <v>48</v>
+      </c>
+      <c r="T43" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="U43" t="n">
+        <v>56.53</v>
+      </c>
+      <c r="V43" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="W43" t="n">
+        <v>50</v>
+      </c>
+      <c r="X43" t="n">
+        <v>48.83</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>60.73</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>63.33</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>58.96</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>8.96</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="AH43" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>55.17</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>56.23</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>59.63</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>58.52</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>55.21</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX43" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>60.83</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>60</v>
+      </c>
+      <c r="BI43" t="n">
+        <v>67.27</v>
+      </c>
+      <c r="BJ43" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="BK43" t="n">
+        <v>68.18</v>
+      </c>
+      <c r="BL43" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="BM43" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -33454,6 +35802,237 @@
       </c>
       <c r="Y40" t="n">
         <v>55.91</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B41" t="n">
+        <v>67</v>
+      </c>
+      <c r="C41" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="D41" t="n">
+        <v>79.58</v>
+      </c>
+      <c r="E41" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="F41" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H41" t="n">
+        <v>50.86</v>
+      </c>
+      <c r="I41" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="J41" t="n">
+        <v>54.32</v>
+      </c>
+      <c r="K41" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="L41" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N41" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="O41" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="P41" t="n">
+        <v>59.38</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="R41" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="S41" t="n">
+        <v>8.39</v>
+      </c>
+      <c r="T41" t="n">
+        <v>72.09</v>
+      </c>
+      <c r="U41" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="V41" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="W41" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="X41" t="n">
+        <v>8.89</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B42" t="n">
+        <v>70.09</v>
+      </c>
+      <c r="C42" t="n">
+        <v>16.02</v>
+      </c>
+      <c r="D42" t="n">
+        <v>76.44</v>
+      </c>
+      <c r="E42" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="F42" t="n">
+        <v>38.89</v>
+      </c>
+      <c r="G42" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="H42" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J42" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="K42" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="L42" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="M42" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="N42" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="O42" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="P42" t="n">
+        <v>58.14</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="R42" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T42" t="n">
+        <v>70.28</v>
+      </c>
+      <c r="U42" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="V42" t="n">
+        <v>77.28</v>
+      </c>
+      <c r="W42" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="X42" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>11.55</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B43" t="n">
+        <v>70.34</v>
+      </c>
+      <c r="C43" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="D43" t="n">
+        <v>75.51</v>
+      </c>
+      <c r="E43" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="F43" t="n">
+        <v>30</v>
+      </c>
+      <c r="G43" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="H43" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="I43" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="J43" t="n">
+        <v>58.61</v>
+      </c>
+      <c r="K43" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="L43" t="n">
+        <v>45.56</v>
+      </c>
+      <c r="M43" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="N43" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="O43" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="P43" t="n">
+        <v>56.58</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="R43" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="T43" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="V43" t="n">
+        <v>64.67</v>
+      </c>
+      <c r="W43" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="X43" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>20.28</v>
       </c>
     </row>
   </sheetData>
@@ -40794,6 +43373,552 @@
         <v>0</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>46217</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>46217</v>
+      </c>
+      <c r="H41" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="I41" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="M41" t="n">
+        <v>22.01</v>
+      </c>
+      <c r="N41" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="O41" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="P41" t="n">
+        <v>9.62</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="R41" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="T41" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="U41" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="V41" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="W41" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="X41" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="Z41" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="AG41" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AN41" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU41" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BB41" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="H42" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="I42" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="M42" t="n">
+        <v>8.61</v>
+      </c>
+      <c r="N42" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="O42" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="P42" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="S42" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="T42" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="U42" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="V42" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="W42" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="X42" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="AG42" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="AN42" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="AU42" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BB42" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E43" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="H43" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="I43" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="J43" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O43" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="P43" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="T43" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="V43" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>8.13</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>9.21</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="AG43" s="3" t="n">
+        <v>46268</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN43" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>9.21</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="AU43" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB43" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -44361,6 +47486,264 @@
       </c>
       <c r="AB41" t="n">
         <v>0.61</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>46217</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>46217</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I42" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="J42" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="L42" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="M42" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="O42" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="P42" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="U42" t="n">
+        <v>15.61</v>
+      </c>
+      <c r="V42" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>2.64</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C43" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="F43" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="G43" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="I43" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="J43" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L43" t="n">
+        <v>9.87</v>
+      </c>
+      <c r="M43" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="O43" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="P43" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="R43" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="U43" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V43" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C44" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="F44" t="n">
+        <v>9.03</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I44" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="L44" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="O44" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="P44" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="Q44" s="3" t="n">
+        <v>46268</v>
+      </c>
+      <c r="R44" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="U44" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="V44" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Z44" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.56</v>
       </c>
     </row>
   </sheetData>
@@ -57213,6 +60596,426 @@
         <v>100</v>
       </c>
       <c r="AT98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B99" s="3" t="n">
+        <v>46217</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>100</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>46217</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>10</v>
+      </c>
+      <c r="J99" t="n">
+        <v>90</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>100</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" t="n">
+        <v>100</v>
+      </c>
+      <c r="U99" t="n">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="W99" t="n">
+        <v>0</v>
+      </c>
+      <c r="X99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>93.33</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="AA99" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF99" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="AK99" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AQ99" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="AR99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS99" t="n">
+        <v>80</v>
+      </c>
+      <c r="AT99" t="n">
+        <v>13.33</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B100" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>100</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>100</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>92.86</v>
+      </c>
+      <c r="P100" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="Q100" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="T100" t="n">
+        <v>92.31</v>
+      </c>
+      <c r="U100" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="W100" t="n">
+        <v>0</v>
+      </c>
+      <c r="X100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>86.67</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="AA100" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK100" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP100" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="AQ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR100" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="AS100" t="n">
+        <v>92.86</v>
+      </c>
+      <c r="AT100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B101" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>100</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>90</v>
+      </c>
+      <c r="K101" t="n">
+        <v>10</v>
+      </c>
+      <c r="L101" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>100</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="S101" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" t="n">
+        <v>85.71</v>
+      </c>
+      <c r="U101" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="V101" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="W101" t="n">
+        <v>0</v>
+      </c>
+      <c r="X101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>78.57</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="AA101" s="3" t="n">
+        <v>46268</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>93.33</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>92.86</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="AP101" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="AQ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS101" t="n">
+        <v>100</v>
+      </c>
+      <c r="AT101" t="n">
         <v>0</v>
       </c>
     </row>
@@ -60940,6 +64743,357 @@
         <v>1.57</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C34" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E34" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>32.71</v>
+      </c>
+      <c r="J34" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="K34" t="n">
+        <v>23.71</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="M34" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O34" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="P34"/>
+      <c r="Q34" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="R34"/>
+      <c r="S34" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T34"/>
+      <c r="U34" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="V34" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="W34" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="X34" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>27.34</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>16.72</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C35" t="n">
+        <v>16.19</v>
+      </c>
+      <c r="D35" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="E35" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I35" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="J35" t="n">
+        <v>8.22</v>
+      </c>
+      <c r="K35" t="n">
+        <v>18.27</v>
+      </c>
+      <c r="L35" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="O35" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="V35" t="n">
+        <v>20.95</v>
+      </c>
+      <c r="W35" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="X35" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>8.03</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C36" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="D36" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="E36" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I36" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="J36" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="K36" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="L36" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="O36" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="P36" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="V36" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="W36" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -62379,6 +66533,138 @@
         <v>3.07</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C34" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="D34" t="n">
+        <v>8.53</v>
+      </c>
+      <c r="E34" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="F34" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" t="n">
+        <v>22.26</v>
+      </c>
+      <c r="J34" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="K34" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="L34" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C35" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="E35" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="F35" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I35" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="J35" t="n">
+        <v>9.29</v>
+      </c>
+      <c r="K35" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="L35" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C36" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="D36" t="n">
+        <v>9.22</v>
+      </c>
+      <c r="E36" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="I36" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="J36" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="K36" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="L36" t="n">
+        <v>8.89</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
